--- a/nodes_source_analyses/energy/transport/transport_motorcycle_using_electricity.converter.xlsx
+++ b/nodes_source_analyses/energy/transport/transport_motorcycle_using_electricity.converter.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="28810"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10621"/>
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michieldenhaan/Projects/etdataset/nodes_source_analyses/transport/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robin/Desktop/Quintel/etdataset/nodes_source_analyses/energy/transport/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A62666-318D-9B45-979B-5ED8877413B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7520" yWindow="480" windowWidth="43680" windowHeight="26900" tabRatio="762" activeTab="4"/>
+    <workbookView xWindow="33260" yWindow="1260" windowWidth="38400" windowHeight="19460" tabRatio="762" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover sheet" sheetId="14" r:id="rId1"/>
@@ -36,10 +37,21 @@
     <definedName name="Wp_to_kWp">#REF!</definedName>
     <definedName name="WP_to_MWp">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="150001" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr defaultImageDpi="32767"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
@@ -49,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="74">
   <si>
     <t>Source</t>
   </si>
@@ -163,9 +175,6 @@
   </si>
   <si>
     <t>Parameter</t>
-  </si>
-  <si>
-    <t>cedelft-ecn-tno</t>
   </si>
   <si>
     <t>jbhunt</t>
@@ -199,24 +208,12 @@
     <t>2017</t>
   </si>
   <si>
-    <t>vehicle km</t>
-  </si>
-  <si>
-    <t>mln vehicle km</t>
-  </si>
-  <si>
     <t>transport_bus_using_compressed_natural_gas.converter.ad</t>
   </si>
   <si>
     <t>CBS</t>
   </si>
   <si>
-    <t>passenger km</t>
-  </si>
-  <si>
-    <t>passenger km/vehicle km</t>
-  </si>
-  <si>
     <t>passenger km/MJ</t>
   </si>
   <si>
@@ -235,15 +232,6 @@
     <t>pkm/MJ</t>
   </si>
   <si>
-    <t>IEA</t>
-  </si>
-  <si>
-    <t>Europe</t>
-  </si>
-  <si>
-    <t>https://www.google.nl/url?sa=t&amp;rct=j&amp;q=&amp;esrc=s&amp;source=web&amp;cd=2&amp;ved=0ahUKEwim4ZyH5rPXAhWFDMAKHfPIA_gQFggrMAE&amp;url=https%3A%2F%2Fiea-etsap.org%2FE-TechDS%2FPDF%2FT19_2-3W_GG_Jan2013_final_GSOK.pdf&amp;usg=AOvVaw0tqWbgNBbWzeslGWhsDSFh</t>
-  </si>
-  <si>
     <t>Moped</t>
   </si>
   <si>
@@ -253,9 +241,6 @@
     <t>km</t>
   </si>
   <si>
-    <t>Weighted average</t>
-  </si>
-  <si>
     <t>Vehicle kilometers motorcycles</t>
   </si>
   <si>
@@ -271,44 +256,57 @@
     <t>pkm/vkm</t>
   </si>
   <si>
-    <t>mln passenger km</t>
-  </si>
-  <si>
-    <t>Note: CBS reports 1,1 mld passenger kilometers for mopeds/scooters but 2,3 mld vehicle kilometers. Therefore, we calculate passenger kms by multiplying motorcycle and moped vehicle kms (CBS) by their respective occupancy rates (CE Delft)</t>
-  </si>
-  <si>
-    <t>IEA (efficiencies)</t>
-  </si>
-  <si>
     <t>CBS (vehicle kms)</t>
   </si>
   <si>
     <t>CE Delft (pkm/vkm)</t>
   </si>
   <si>
-    <t>Passenger kilometers motorcyles and mopeds/scooters</t>
-  </si>
-  <si>
     <t>Motorcycle</t>
   </si>
   <si>
-    <t>Note: IEA, took efficiency to be 0.045 instead of 0.06 because numbers are based on Chinese market, not Europe</t>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t> https://ce.nl/wp-content/uploads/2025/02/CE_Delft_210506_STREAM_Personenvervoer_2024_Def.pdf</t>
+  </si>
+  <si>
+    <t>Weighted average efficiency</t>
+  </si>
+  <si>
+    <t>Weighted average pkm/vkm</t>
+  </si>
+  <si>
+    <t>Passenger kilometers/vkm motorcyles and mopeds</t>
+  </si>
+  <si>
+    <t>CE Delft p. 32,33 (MJ/km)</t>
+  </si>
+  <si>
+    <t>Robin de Smit</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="30">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Lettertype hoofdtekst"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -501,13 +499,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -797,439 +788,425 @@
   </borders>
   <cellStyleXfs count="251">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="20" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="21" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="15" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="15" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="10" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="25" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="26" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="21" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="21" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="20" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="20" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="25" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="25" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="29" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="251">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -1490,123 +1467,81 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>508000</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>665502</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>396240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>306766</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>1595120</xdr:rowOff>
     </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="10" name="Group 9"/>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="Picture 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000013000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="10312400" y="9245600"/>
-          <a:ext cx="9817100" cy="3035300"/>
-          <a:chOff x="9231573" y="32137067"/>
-          <a:chExt cx="12902777" cy="4417646"/>
+          <a:off x="16718302" y="4876800"/>
+          <a:ext cx="7809904" cy="1198880"/>
         </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="11" name="Picture 10"/>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="9231573" y="32137067"/>
-            <a:ext cx="12902777" cy="4417646"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="12" name="Rectangle 11"/>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="13300038" y="35068579"/>
-            <a:ext cx="1173710" cy="378631"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
-            <a:solidFill>
-              <a:srgbClr val="FFC000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="3">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="2">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr lang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>4178300</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>507999</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>325120</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>428176</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>91820</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>287584</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>3299460</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="Picture 16"/>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1619,122 +1554,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13982700" y="368300"/>
-          <a:ext cx="5749476" cy="4003420"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>469899</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>126999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>687324</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="Picture 17"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15925799" y="342899"/>
-          <a:ext cx="7645401" cy="4827525"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>533400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>520700</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>1553793</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="Picture 18"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16738600" y="5016500"/>
-          <a:ext cx="6667500" cy="1020393"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>508000</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>558800</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>3299460</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9486900" y="5041900"/>
-          <a:ext cx="6324600" cy="2740660"/>
+          <a:off x="9479279" y="4805680"/>
+          <a:ext cx="6861105" cy="2974340"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1754,17 +1575,23 @@
       <xdr:col>23</xdr:col>
       <xdr:colOff>711200</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>147923</xdr:rowOff>
+      <xdr:rowOff>188563</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5"/>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1781,12 +1608,359 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>433990</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>31970</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>375745</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>15767</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55C82128-B611-8B10-8F62-FCA8CFBD53A2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10210800" y="2955160"/>
+          <a:ext cx="6959600" cy="1231900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>459826</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>76638</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>744481</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>3462</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4897A951-806E-5FC5-570E-190D26AAF65D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10236636" y="1751724"/>
+          <a:ext cx="7302500" cy="1168400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>503620</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>43794</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>3788103</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>164225</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Rectangle 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AAD5D444-8630-0F3D-E361-D829C38DC8B0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10297860" y="2492354"/>
+          <a:ext cx="3284483" cy="323631"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>470776</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>164224</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>4280776</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>76637</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Rectangle 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E73DD4F-866C-9E4C-8D9C-F7FD7661FECF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10247586" y="3711465"/>
+          <a:ext cx="3810000" cy="328448"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>314960</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>1313794</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>425143</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>1637425</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="Rectangle 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2799BD00-905B-2148-8439-CF32842DD9AD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15544800" y="5794354"/>
+          <a:ext cx="933143" cy="323631"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>711200</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>1181715</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>821383</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>1473201</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="Rectangle 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBEDDDF9-7766-3D47-9918-415C7C7EFCCD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18348960" y="5662275"/>
+          <a:ext cx="933143" cy="291486"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Cover Sheet"/>
       <sheetName val="Changelog"/>
@@ -2218,53 +2392,55 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet1" enableFormatConditionsCalculation="0">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1">
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:C23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="3.1640625" style="22" customWidth="1"/>
+    <col min="1" max="1" width="3.1640625" style="21" customWidth="1"/>
     <col min="2" max="2" width="11.5" style="14" customWidth="1"/>
     <col min="3" max="3" width="38.5" style="14" customWidth="1"/>
     <col min="4" max="16384" width="10.83203125" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="18"/>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-    </row>
-    <row r="2" spans="1:3" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="19" customFormat="1">
+      <c r="A1" s="17"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+    </row>
+    <row r="2" spans="1:3" ht="21">
       <c r="A2" s="1"/>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="21"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C2" s="20"/>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="1"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="1"/>
       <c r="B5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="5"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C5" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="1"/>
       <c r="B6" s="6" t="s">
         <v>12</v>
@@ -2273,117 +2449,117 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3">
       <c r="A7" s="1"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3">
       <c r="A8" s="1"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3">
       <c r="A9" s="1"/>
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="47"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C9" s="44"/>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" s="1"/>
-      <c r="B10" s="48"/>
-      <c r="C10" s="49"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B10" s="45"/>
+      <c r="C10" s="46"/>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" s="1"/>
-      <c r="B11" s="48" t="s">
+      <c r="B11" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="50" t="s">
+      <c r="C11" s="47" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="17" thickBot="1">
       <c r="A12" s="1"/>
-      <c r="B12" s="48"/>
+      <c r="B12" s="45"/>
       <c r="C12" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="17" thickBot="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="48"/>
-      <c r="C13" s="51" t="s">
+      <c r="B13" s="45"/>
+      <c r="C13" s="48" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3">
       <c r="A14" s="1"/>
-      <c r="B14" s="48"/>
-      <c r="C14" s="49" t="s">
+      <c r="B14" s="45"/>
+      <c r="C14" s="46" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3">
       <c r="A15" s="1"/>
-      <c r="B15" s="48"/>
-      <c r="C15" s="49"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B15" s="45"/>
+      <c r="C15" s="46"/>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="1"/>
-      <c r="B16" s="48" t="s">
+      <c r="B16" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="52" t="s">
+      <c r="C16" s="49" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3">
       <c r="A17" s="1"/>
-      <c r="B17" s="48"/>
-      <c r="C17" s="53" t="s">
+      <c r="B17" s="45"/>
+      <c r="C17" s="50" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3">
       <c r="A18" s="1"/>
-      <c r="B18" s="48"/>
-      <c r="C18" s="54" t="s">
+      <c r="B18" s="45"/>
+      <c r="C18" s="51" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3">
       <c r="A19" s="1"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="55" t="s">
+      <c r="B19" s="45"/>
+      <c r="C19" s="52" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3">
       <c r="A20" s="1"/>
-      <c r="B20" s="56"/>
-      <c r="C20" s="57" t="s">
+      <c r="B20" s="53"/>
+      <c r="C20" s="54" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3">
       <c r="A21" s="1"/>
-      <c r="B21" s="56"/>
-      <c r="C21" s="58" t="s">
+      <c r="B21" s="53"/>
+      <c r="C21" s="55" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3">
       <c r="A22" s="1"/>
-      <c r="B22" s="56"/>
-      <c r="C22" s="59" t="s">
+      <c r="B22" s="53"/>
+      <c r="C22" s="56" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B23" s="56"/>
-      <c r="C23" s="60" t="s">
+    <row r="23" spans="1:3">
+      <c r="B23" s="53"/>
+      <c r="C23" s="57" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2394,71 +2570,63 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet2" enableFormatConditionsCalculation="0">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr codeName="Sheet2">
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="B1:J19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="B2:J19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="3.1640625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="3.5" style="26" customWidth="1"/>
-    <col min="3" max="3" width="33.83203125" style="26" customWidth="1"/>
-    <col min="4" max="4" width="12.5" style="26" customWidth="1"/>
-    <col min="5" max="5" width="17.5" style="26" customWidth="1"/>
-    <col min="6" max="6" width="4.5" style="26" customWidth="1"/>
-    <col min="7" max="7" width="44.1640625" style="26" customWidth="1"/>
-    <col min="8" max="8" width="2.5" style="26" customWidth="1"/>
-    <col min="9" max="9" width="42.5" style="26" customWidth="1"/>
-    <col min="10" max="10" width="3.5" style="26" customWidth="1"/>
-    <col min="11" max="16384" width="10.83203125" style="26"/>
+    <col min="1" max="1" width="3.1640625" style="25" customWidth="1"/>
+    <col min="2" max="2" width="3.5" style="25" customWidth="1"/>
+    <col min="3" max="3" width="33.83203125" style="25" customWidth="1"/>
+    <col min="4" max="4" width="12.5" style="25" customWidth="1"/>
+    <col min="5" max="5" width="17.5" style="25" customWidth="1"/>
+    <col min="6" max="6" width="4.5" style="25" customWidth="1"/>
+    <col min="7" max="7" width="44.1640625" style="25" customWidth="1"/>
+    <col min="8" max="8" width="2.5" style="25" customWidth="1"/>
+    <col min="9" max="9" width="42.5" style="25" customWidth="1"/>
+    <col min="10" max="10" width="3.5" style="25" customWidth="1"/>
+    <col min="11" max="16384" width="10.83203125" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-    </row>
-    <row r="2" spans="2:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="114" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="116"/>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B3" s="117"/>
-      <c r="C3" s="118"/>
-      <c r="D3" s="118"/>
-      <c r="E3" s="118"/>
-      <c r="F3" s="118"/>
-      <c r="G3" s="119"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B4" s="117"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="119"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B5" s="120"/>
-      <c r="C5" s="121"/>
-      <c r="D5" s="121"/>
-      <c r="E5" s="121"/>
-      <c r="F5" s="121"/>
-      <c r="G5" s="122"/>
-    </row>
-    <row r="6" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D6" s="27"/>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B7" s="28"/>
+    <row r="2" spans="2:10" ht="16" customHeight="1">
+      <c r="B2" s="102" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="104"/>
+    </row>
+    <row r="3" spans="2:10">
+      <c r="B3" s="105"/>
+      <c r="C3" s="106"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="106"/>
+      <c r="F3" s="106"/>
+      <c r="G3" s="107"/>
+    </row>
+    <row r="4" spans="2:10">
+      <c r="B4" s="105"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="107"/>
+    </row>
+    <row r="5" spans="2:10">
+      <c r="B5" s="108"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="109"/>
+      <c r="E5" s="109"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="110"/>
+    </row>
+    <row r="6" spans="2:10" ht="17" thickBot="1"/>
+    <row r="7" spans="2:10">
+      <c r="B7" s="26"/>
       <c r="C7" s="13"/>
       <c r="D7" s="13"/>
       <c r="E7" s="13"/>
@@ -2466,128 +2634,108 @@
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
       <c r="I7" s="13"/>
-      <c r="J7" s="29"/>
-    </row>
-    <row r="8" spans="2:10" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="61"/>
-      <c r="C8" s="62" t="s">
+      <c r="J7" s="27"/>
+    </row>
+    <row r="8" spans="2:10" s="11" customFormat="1">
+      <c r="B8" s="58"/>
+      <c r="C8" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="63" t="s">
+      <c r="D8" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="62" t="s">
+      <c r="E8" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="62"/>
-      <c r="G8" s="62" t="s">
+      <c r="F8" s="59"/>
+      <c r="G8" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="H8" s="62"/>
-      <c r="I8" s="62" t="s">
+      <c r="H8" s="59"/>
+      <c r="I8" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="J8" s="64"/>
-    </row>
-    <row r="9" spans="2:10" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="J8" s="61"/>
+    </row>
+    <row r="9" spans="2:10" s="11" customFormat="1">
       <c r="B9" s="16"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="D9" s="23"/>
       <c r="J9" s="12"/>
     </row>
-    <row r="10" spans="2:10" s="17" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" s="11" customFormat="1" ht="17" thickBot="1">
       <c r="B10" s="16"/>
       <c r="C10" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="24"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="D10" s="23"/>
       <c r="J10" s="12"/>
     </row>
-    <row r="11" spans="2:10" s="17" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:10" s="11" customFormat="1" ht="17" thickBot="1">
       <c r="B11" s="16"/>
-      <c r="C11" s="88" t="s">
-        <v>59</v>
+      <c r="C11" s="83" t="s">
+        <v>54</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" s="25">
+        <v>55</v>
+      </c>
+      <c r="E11" s="24">
         <f>'Research data'!E7</f>
-        <v>9.1047924248184948</v>
-      </c>
-      <c r="F11" s="30"/>
-      <c r="G11" s="94" t="s">
-        <v>46</v>
-      </c>
-      <c r="H11" s="23"/>
-      <c r="I11" s="93" t="s">
-        <v>38</v>
+        <v>2.5677050000000001</v>
+      </c>
+      <c r="F11" s="28"/>
+      <c r="G11" s="88"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="112" t="s">
+        <v>51</v>
       </c>
       <c r="J11" s="12"/>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B12" s="31"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="65"/>
-      <c r="E12" s="66"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="67"/>
-      <c r="J12" s="68"/>
-    </row>
-    <row r="13" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="31"/>
+    <row r="12" spans="2:10">
+      <c r="B12" s="29"/>
+      <c r="D12" s="62"/>
+      <c r="E12" s="63"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="65"/>
+    </row>
+    <row r="13" spans="2:10" ht="17" thickBot="1">
+      <c r="B13" s="29"/>
       <c r="C13" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="D13" s="65"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="67"/>
-      <c r="J13" s="68"/>
-    </row>
-    <row r="14" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="31"/>
-      <c r="C14" s="30" t="s">
+      <c r="D13" s="62"/>
+      <c r="E13" s="63"/>
+      <c r="I13" s="64"/>
+      <c r="J13" s="65"/>
+    </row>
+    <row r="14" spans="2:10" ht="17" thickBot="1">
+      <c r="B14" s="29"/>
+      <c r="C14" s="28" t="s">
         <v>19</v>
       </c>
       <c r="D14" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="30">
         <v>0</v>
       </c>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="25"/>
-      <c r="J14" s="68"/>
-    </row>
-    <row r="15" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="33"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="35"/>
-    </row>
-    <row r="19" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="65"/>
+    </row>
+    <row r="15" spans="2:10" ht="17" thickBot="1">
+      <c r="B15" s="31"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="33"/>
+    </row>
+    <row r="19" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:G5"/>
@@ -2598,74 +2746,73 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet3" enableFormatConditionsCalculation="0">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr codeName="Sheet3">
     <tabColor theme="6" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="B2:K8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="2" width="4.5" style="36" customWidth="1"/>
-    <col min="3" max="3" width="33.1640625" style="36" customWidth="1"/>
-    <col min="4" max="4" width="11.5" style="36" customWidth="1"/>
-    <col min="5" max="5" width="9.5" style="36" customWidth="1"/>
-    <col min="6" max="6" width="2.5" style="36" customWidth="1"/>
-    <col min="7" max="7" width="10.5" style="36" customWidth="1"/>
-    <col min="8" max="8" width="2.1640625" style="36" customWidth="1"/>
-    <col min="9" max="9" width="17.1640625" style="36" customWidth="1"/>
-    <col min="10" max="10" width="2.83203125" style="36" customWidth="1"/>
-    <col min="11" max="11" width="59.1640625" style="36" customWidth="1"/>
-    <col min="12" max="16384" width="10.83203125" style="36"/>
+    <col min="1" max="2" width="4.5" style="34" customWidth="1"/>
+    <col min="3" max="3" width="33.1640625" style="34" customWidth="1"/>
+    <col min="4" max="4" width="11.5" style="34" customWidth="1"/>
+    <col min="5" max="5" width="9.5" style="34" customWidth="1"/>
+    <col min="6" max="6" width="2.5" style="34" customWidth="1"/>
+    <col min="7" max="7" width="10.5" style="34" customWidth="1"/>
+    <col min="8" max="8" width="2.1640625" style="34" customWidth="1"/>
+    <col min="9" max="9" width="17.1640625" style="34" customWidth="1"/>
+    <col min="10" max="10" width="2.83203125" style="34" customWidth="1"/>
+    <col min="11" max="11" width="59.1640625" style="34" customWidth="1"/>
+    <col min="12" max="16384" width="10.83203125" style="34"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-    </row>
-    <row r="4" spans="2:11" s="17" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:11" ht="17" thickBot="1"/>
+    <row r="3" spans="2:11">
+      <c r="B3" s="35"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+    </row>
+    <row r="4" spans="2:11" s="11" customFormat="1">
       <c r="B4" s="16"/>
-      <c r="C4" s="69" t="s">
+      <c r="C4" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="69" t="s">
+      <c r="D4" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="69" t="s">
+      <c r="E4" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69" t="s">
+      <c r="F4" s="66"/>
+      <c r="G4" s="66" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="J4" s="66"/>
+      <c r="K4" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69" t="s">
-        <v>61</v>
-      </c>
-      <c r="J4" s="69"/>
-      <c r="K4" s="69" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="39"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="K5" s="44"/>
-    </row>
-    <row r="6" spans="2:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="39"/>
+    </row>
+    <row r="5" spans="2:11" ht="18" customHeight="1">
+      <c r="B5" s="37"/>
+      <c r="C5" s="39"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="K5" s="41"/>
+    </row>
+    <row r="6" spans="2:11" ht="18" customHeight="1" thickBot="1">
+      <c r="B6" s="37"/>
       <c r="C6" s="10" t="s">
         <v>36</v>
       </c>
@@ -2673,40 +2820,35 @@
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
-      <c r="H6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="43"/>
-    </row>
-    <row r="7" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="39"/>
-      <c r="C7" s="90" t="s">
-        <v>59</v>
-      </c>
-      <c r="D7" s="91" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" s="92">
+      <c r="K6" s="40"/>
+    </row>
+    <row r="7" spans="2:11" ht="17" thickBot="1">
+      <c r="B7" s="37"/>
+      <c r="C7" s="85" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="86" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="87">
         <f>I7</f>
-        <v>9.1047924248184948</v>
-      </c>
-      <c r="F7" s="41"/>
-      <c r="G7" s="82"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="92">
-        <f>Notes!E34</f>
-        <v>9.1047924248184948</v>
-      </c>
-      <c r="J7" s="40"/>
-      <c r="K7" s="45"/>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B8" s="39"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="K8" s="44"/>
+        <v>2.5677050000000001</v>
+      </c>
+      <c r="F7" s="38"/>
+      <c r="G7" s="77"/>
+      <c r="I7" s="87">
+        <f>Notes!E17</f>
+        <v>2.5677050000000001</v>
+      </c>
+      <c r="K7" s="42"/>
+    </row>
+    <row r="8" spans="2:11">
+      <c r="B8" s="37"/>
+      <c r="C8" s="39"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="K8" s="41"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2715,39 +2857,39 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet4" enableFormatConditionsCalculation="0">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr codeName="Sheet4">
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="B1:J12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="33.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="33.1640625" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="3.1640625" style="70" customWidth="1"/>
-    <col min="2" max="2" width="4" style="70" customWidth="1"/>
-    <col min="3" max="3" width="47.33203125" style="70" customWidth="1"/>
-    <col min="4" max="4" width="16.1640625" style="70" customWidth="1"/>
-    <col min="5" max="5" width="10.1640625" style="70" customWidth="1"/>
-    <col min="6" max="7" width="13.1640625" style="70" customWidth="1"/>
-    <col min="8" max="8" width="12.5" style="71" customWidth="1"/>
-    <col min="9" max="9" width="32.5" style="71" customWidth="1"/>
-    <col min="10" max="10" width="98.5" style="70" customWidth="1"/>
-    <col min="11" max="16384" width="33.1640625" style="70"/>
+    <col min="1" max="1" width="3.1640625" style="67" customWidth="1"/>
+    <col min="2" max="2" width="4" style="67" customWidth="1"/>
+    <col min="3" max="3" width="47.33203125" style="67" customWidth="1"/>
+    <col min="4" max="4" width="16.1640625" style="67" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" style="67" customWidth="1"/>
+    <col min="6" max="7" width="13.1640625" style="67" customWidth="1"/>
+    <col min="8" max="8" width="12.5" style="68" customWidth="1"/>
+    <col min="9" max="9" width="32.5" style="68" customWidth="1"/>
+    <col min="10" max="10" width="98.5" style="67" customWidth="1"/>
+    <col min="11" max="16384" width="33.1640625" style="67"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B2" s="72"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="73"/>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B3" s="75"/>
+    <row r="1" spans="2:10" ht="17" thickBot="1"/>
+    <row r="2" spans="2:10">
+      <c r="B2" s="69"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="70"/>
+    </row>
+    <row r="3" spans="2:10">
+      <c r="B3" s="72"/>
       <c r="C3" s="11" t="s">
         <v>14</v>
       </c>
@@ -2755,153 +2897,139 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="77"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B4" s="75"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="78"/>
-      <c r="I4" s="78"/>
-      <c r="J4" s="77"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B5" s="79"/>
-      <c r="C5" s="62" t="s">
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+    </row>
+    <row r="4" spans="2:10">
+      <c r="B4" s="72"/>
+    </row>
+    <row r="5" spans="2:10">
+      <c r="B5" s="74"/>
+      <c r="C5" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="62" t="s">
+      <c r="D5" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="62" t="s">
+      <c r="E5" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="62" t="s">
+      <c r="F5" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="62" t="s">
+      <c r="G5" s="59" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" s="75" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="75" t="s">
         <v>42</v>
       </c>
-      <c r="H5" s="80" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="80" t="s">
-        <v>43</v>
-      </c>
-      <c r="J5" s="62" t="s">
+      <c r="J5" s="59" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B6" s="75"/>
-      <c r="C6" s="95" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="109" t="s">
+    <row r="6" spans="2:10">
+      <c r="B6" s="72"/>
+      <c r="C6" s="89" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="111" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="111" t="s">
+        <v>67</v>
+      </c>
+      <c r="F6" s="67">
+        <v>2024</v>
+      </c>
+      <c r="G6" s="67">
+        <v>2024</v>
+      </c>
+      <c r="H6" s="67">
+        <v>2026</v>
+      </c>
+      <c r="I6" s="82"/>
+      <c r="J6" s="67" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10">
+      <c r="B7" s="72"/>
+      <c r="C7" s="76" t="s">
+        <v>2</v>
+      </c>
+      <c r="H7" s="67"/>
+      <c r="I7" s="67"/>
+    </row>
+    <row r="9" spans="2:10" s="92" customFormat="1">
+      <c r="B9" s="93"/>
+      <c r="C9" s="94"/>
+      <c r="H9" s="95"/>
+      <c r="I9" s="95"/>
+    </row>
+    <row r="10" spans="2:10">
+      <c r="C10" s="96" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="96" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="96" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="67">
+        <v>2015</v>
+      </c>
+      <c r="H10" s="99" t="s">
+        <v>47</v>
+      </c>
+      <c r="J10" s="90" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10">
+      <c r="C11" s="96" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="96" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="96" t="s">
+        <v>5</v>
+      </c>
+      <c r="G11" s="67">
+        <v>2015</v>
+      </c>
+      <c r="H11" s="99" t="s">
+        <v>47</v>
+      </c>
+      <c r="J11" s="90" t="s">
         <v>61</v>
       </c>
-      <c r="E6" s="109" t="s">
-        <v>62</v>
-      </c>
-      <c r="F6" s="77">
-        <v>2013</v>
-      </c>
-      <c r="G6" s="77">
-        <v>2013</v>
-      </c>
-      <c r="H6" s="77">
-        <v>2017</v>
-      </c>
-      <c r="I6" s="87"/>
-      <c r="J6" s="77" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B7" s="75"/>
-      <c r="C7" s="81" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="77"/>
-      <c r="E7" s="77"/>
-      <c r="F7" s="77"/>
-      <c r="G7" s="77"/>
-      <c r="H7" s="77"/>
-      <c r="I7" s="77"/>
-      <c r="J7" s="77"/>
-    </row>
-    <row r="9" spans="2:10" s="103" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="104"/>
-      <c r="C9" s="105"/>
-      <c r="H9" s="106"/>
-      <c r="I9" s="106"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="C10" s="108" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" s="108" t="s">
+    </row>
+    <row r="12" spans="2:10">
+      <c r="C12" s="111" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="96" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="96" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="67">
+        <v>2014</v>
+      </c>
+      <c r="H12" s="99" t="s">
+        <v>47</v>
+      </c>
+      <c r="I12" s="96" t="s">
         <v>52</v>
       </c>
-      <c r="E10" s="108" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="70">
-        <v>2015</v>
-      </c>
-      <c r="H10" s="113" t="s">
-        <v>48</v>
-      </c>
-      <c r="J10" s="107" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="C11" s="108" t="s">
-        <v>69</v>
-      </c>
-      <c r="D11" s="108" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="108" t="s">
-        <v>5</v>
-      </c>
-      <c r="G11" s="70">
-        <v>2015</v>
-      </c>
-      <c r="H11" s="113" t="s">
-        <v>48</v>
-      </c>
-      <c r="J11" s="107" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="C12" s="108" t="s">
-        <v>78</v>
-      </c>
-      <c r="D12" s="108" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="108" t="s">
-        <v>5</v>
-      </c>
-      <c r="G12" s="70">
-        <v>2014</v>
-      </c>
-      <c r="H12" s="113" t="s">
-        <v>48</v>
-      </c>
-      <c r="I12" s="108" t="s">
-        <v>57</v>
-      </c>
-      <c r="J12" s="108" t="s">
-        <v>58</v>
+      <c r="J12" s="96" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -2911,536 +3039,448 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:AD83"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="5.5" style="83" customWidth="1"/>
-    <col min="2" max="2" width="4.5" style="83" customWidth="1"/>
-    <col min="3" max="3" width="30.33203125" style="83" customWidth="1"/>
-    <col min="4" max="4" width="27.5" style="83" customWidth="1"/>
-    <col min="5" max="5" width="17.5" style="83" customWidth="1"/>
-    <col min="6" max="9" width="10.83203125" style="83"/>
-    <col min="10" max="10" width="71.33203125" style="83" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" style="83"/>
-    <col min="12" max="12" width="10" style="83" customWidth="1"/>
-    <col min="13" max="16384" width="10.83203125" style="83"/>
+    <col min="1" max="1" width="5.5" style="78" customWidth="1"/>
+    <col min="2" max="2" width="4.5" style="78" customWidth="1"/>
+    <col min="3" max="3" width="30.33203125" style="78" customWidth="1"/>
+    <col min="4" max="4" width="27.5" style="78" customWidth="1"/>
+    <col min="5" max="5" width="17.5" style="78" customWidth="1"/>
+    <col min="6" max="9" width="10.83203125" style="78"/>
+    <col min="10" max="10" width="71.33203125" style="78" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" style="78"/>
+    <col min="12" max="12" width="10" style="78" customWidth="1"/>
+    <col min="13" max="16384" width="10.83203125" style="78"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:30" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="B2" s="84"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="85"/>
-      <c r="K2" s="85"/>
-      <c r="L2" s="85"/>
-      <c r="M2" s="85"/>
-      <c r="N2" s="85"/>
-      <c r="O2" s="85"/>
-      <c r="P2" s="85"/>
-      <c r="Q2" s="85"/>
-      <c r="R2" s="85"/>
-      <c r="S2" s="85"/>
-      <c r="T2" s="85"/>
-      <c r="U2" s="85"/>
-      <c r="V2" s="85"/>
-      <c r="W2" s="85"/>
-      <c r="X2" s="85"/>
-      <c r="Y2" s="85"/>
-      <c r="Z2" s="85"/>
-      <c r="AA2" s="85"/>
-      <c r="AB2" s="85"/>
-      <c r="AC2" s="85"/>
-      <c r="AD2" s="85"/>
-    </row>
-    <row r="3" spans="2:30" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="61"/>
-      <c r="C3" s="62" t="s">
+    <row r="1" spans="2:30" ht="17" thickBot="1"/>
+    <row r="2" spans="2:30">
+      <c r="B2" s="79"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="80"/>
+      <c r="M2" s="80"/>
+      <c r="N2" s="80"/>
+      <c r="O2" s="80"/>
+      <c r="P2" s="80"/>
+      <c r="Q2" s="80"/>
+      <c r="R2" s="80"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="80"/>
+      <c r="U2" s="80"/>
+      <c r="V2" s="80"/>
+      <c r="W2" s="80"/>
+      <c r="X2" s="80"/>
+      <c r="Y2" s="80"/>
+      <c r="Z2" s="80"/>
+      <c r="AA2" s="80"/>
+      <c r="AB2" s="80"/>
+      <c r="AC2" s="80"/>
+      <c r="AD2" s="80"/>
+    </row>
+    <row r="3" spans="2:30" s="11" customFormat="1">
+      <c r="B3" s="58"/>
+      <c r="C3" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="62" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="62"/>
-    </row>
-    <row r="4" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="B4" s="86"/>
-      <c r="E4" s="108" t="s">
-        <v>46</v>
-      </c>
-      <c r="G4" s="108" t="s">
+      <c r="D3" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="59"/>
+      <c r="L3" s="59"/>
+    </row>
+    <row r="4" spans="2:30">
+      <c r="B4" s="81"/>
+      <c r="E4" s="96" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" s="96" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" s="96" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="2:30">
+      <c r="B5" s="81"/>
+      <c r="C5" s="111" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="96" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="78">
+        <v>0.2</v>
+      </c>
+      <c r="F5" s="96" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="97">
+        <v>2348</v>
+      </c>
+      <c r="H5" s="98" t="s">
+        <v>58</v>
+      </c>
+      <c r="I5" s="98">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J5" s="100"/>
+    </row>
+    <row r="6" spans="2:30">
+      <c r="B6" s="81"/>
+      <c r="C6" s="96" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="100" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" s="78">
+        <v>0.7</v>
+      </c>
+      <c r="F6" s="96" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="97">
+        <v>2127</v>
+      </c>
+      <c r="H6" s="98" t="s">
+        <v>58</v>
+      </c>
+      <c r="I6" s="98">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="2:30">
+      <c r="B7" s="81"/>
+      <c r="C7" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="I4" s="108" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="B5" s="86"/>
-      <c r="C5" s="108" t="s">
-        <v>75</v>
-      </c>
-      <c r="D5" s="108" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" s="83">
-        <f>AVERAGE(0.045)</f>
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="F5" s="108" t="s">
+      <c r="G7" s="97"/>
+      <c r="H7" s="101"/>
+      <c r="I7" s="101"/>
+    </row>
+    <row r="8" spans="2:30">
+      <c r="B8" s="81"/>
+      <c r="D8" s="96"/>
+      <c r="F8" s="96"/>
+      <c r="H8" s="101"/>
+      <c r="I8" s="101"/>
+    </row>
+    <row r="9" spans="2:30">
+      <c r="B9" s="81"/>
+    </row>
+    <row r="10" spans="2:30">
+      <c r="B10" s="81"/>
+    </row>
+    <row r="11" spans="2:30">
+      <c r="B11" s="81"/>
+      <c r="D11" s="111" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="78">
+        <f>AVERAGE(AVERAGE(E5)*G5,AVERAGE(E6)*G6)/AVERAGE(G5,G6)</f>
+        <v>0.43765363128491619</v>
+      </c>
+      <c r="F11" s="84" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="2:30">
+      <c r="B12" s="81"/>
+      <c r="C12" s="84"/>
+      <c r="E12" s="78">
+        <f>1/E11</f>
+        <v>2.284911922389584</v>
+      </c>
+      <c r="F12" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="110">
-        <v>2348</v>
-      </c>
-      <c r="H5" s="111" t="s">
-        <v>66</v>
-      </c>
-      <c r="I5" s="111">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="J5" s="124" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="B6" s="86"/>
-      <c r="C6" s="108" t="s">
-        <v>76</v>
-      </c>
-      <c r="D6" s="124" t="s">
-        <v>79</v>
-      </c>
-      <c r="E6" s="83">
-        <f>AVERAGE(0.14,0.28)</f>
-        <v>0.21000000000000002</v>
-      </c>
-      <c r="F6" s="108" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="110">
-        <v>2127</v>
-      </c>
-      <c r="H6" s="111" t="s">
-        <v>66</v>
-      </c>
-      <c r="I6" s="111">
-        <v>1.1499999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="B7" s="86"/>
-      <c r="C7" s="108" t="s">
-        <v>77</v>
-      </c>
-      <c r="G7" s="110"/>
-      <c r="H7" s="123"/>
-      <c r="I7" s="123"/>
-    </row>
-    <row r="8" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="B8" s="86"/>
-      <c r="D8" s="108"/>
-      <c r="F8" s="108"/>
-      <c r="H8" s="123"/>
-      <c r="I8" s="123"/>
-    </row>
-    <row r="9" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="B9" s="86"/>
-    </row>
-    <row r="10" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="B10" s="86"/>
-    </row>
-    <row r="11" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="B11" s="86"/>
-      <c r="D11" s="108" t="s">
-        <v>67</v>
-      </c>
-      <c r="E11" s="83">
-        <f>AVERAGE(AVERAGE(E5)*G5,AVERAGE(E6)*G6)/AVERAGE(G5,G6)</f>
-        <v>0.12342569832402235</v>
-      </c>
-      <c r="F11" s="89" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="B12" s="86"/>
-      <c r="C12" s="89"/>
-      <c r="E12" s="83">
-        <f>1/E11</f>
-        <v>8.1020404468343195</v>
-      </c>
-      <c r="F12" s="89" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="B13" s="86"/>
-    </row>
-    <row r="14" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="B14" s="86"/>
-    </row>
-    <row r="15" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="B15" s="86"/>
-    </row>
-    <row r="16" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="B16" s="86"/>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B17" s="86"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B18" s="86"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B19" s="86"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B20" s="86"/>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B21" s="86"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B22" s="86"/>
-    </row>
-    <row r="23" spans="2:10" ht="306" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="86"/>
-    </row>
-    <row r="24" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="86"/>
-      <c r="J24" s="108" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10" s="96" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="86"/>
-      <c r="C25" s="97" t="s">
-        <v>52</v>
-      </c>
-      <c r="D25" s="98" t="s">
-        <v>49</v>
-      </c>
-      <c r="E25" s="99">
-        <f>G5+G6</f>
-        <v>4475</v>
-      </c>
-      <c r="F25" s="98" t="s">
-        <v>50</v>
-      </c>
-      <c r="G25" s="98"/>
-      <c r="H25" s="98"/>
-      <c r="I25" s="98"/>
-      <c r="J25" s="98"/>
-    </row>
-    <row r="26" spans="2:10" s="96" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="86"/>
-      <c r="C26" s="97" t="s">
-        <v>56</v>
-      </c>
-      <c r="D26" s="98"/>
-      <c r="E26" s="98">
-        <f>E25*1000000</f>
-        <v>4475000000</v>
-      </c>
-      <c r="F26" s="98" t="s">
-        <v>49</v>
-      </c>
-      <c r="G26" s="98"/>
-      <c r="H26" s="98"/>
-      <c r="I26" s="98"/>
-      <c r="J26" s="98"/>
-    </row>
-    <row r="27" spans="2:10" s="96" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="86"/>
-      <c r="C27" s="98"/>
-      <c r="D27" s="98" t="s">
-        <v>53</v>
-      </c>
-      <c r="E27" s="100">
-        <f>(G5*I5)+(G6*I6)</f>
-        <v>5028.8500000000004</v>
-      </c>
-      <c r="F27" s="98" t="s">
-        <v>73</v>
-      </c>
-      <c r="G27" s="98"/>
-      <c r="H27" s="98"/>
-      <c r="I27" s="98"/>
-      <c r="J27" s="98"/>
-    </row>
-    <row r="28" spans="2:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="86"/>
-      <c r="C28" s="98"/>
-      <c r="D28" s="98"/>
-      <c r="E28" s="101">
-        <f>E27*1000000</f>
-        <v>5028850000</v>
-      </c>
-      <c r="F28" s="98" t="s">
-        <v>53</v>
-      </c>
-      <c r="G28" s="98"/>
-      <c r="H28" s="98"/>
-      <c r="I28" s="98"/>
-      <c r="J28" s="98"/>
-    </row>
-    <row r="29" spans="2:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="86"/>
-      <c r="C29" s="98"/>
-      <c r="D29" s="98"/>
-      <c r="E29" s="98"/>
-      <c r="F29" s="98"/>
-      <c r="G29" s="98"/>
-      <c r="H29" s="98"/>
-      <c r="I29" s="98"/>
-      <c r="J29" s="98"/>
-    </row>
-    <row r="30" spans="2:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="86"/>
-      <c r="C30" s="98"/>
-      <c r="D30" s="98"/>
-      <c r="E30" s="102">
-        <f>E28/E26</f>
+    </row>
+    <row r="13" spans="2:30">
+      <c r="B13" s="81"/>
+    </row>
+    <row r="14" spans="2:30">
+      <c r="B14" s="81"/>
+      <c r="D14" s="111" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" s="78">
+        <f>AVERAGE(AVERAGE(I5)*G5,AVERAGE(I6)*G6)/AVERAGE(G5, G6)</f>
         <v>1.1237653631284916</v>
       </c>
-      <c r="F30" s="98" t="s">
-        <v>54</v>
-      </c>
-      <c r="G30" s="98"/>
-      <c r="H30" s="98"/>
-      <c r="I30" s="98"/>
-      <c r="J30" s="98"/>
-    </row>
-    <row r="31" spans="2:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="86"/>
-      <c r="C31" s="98"/>
-      <c r="D31" s="98"/>
-      <c r="E31" s="98"/>
-      <c r="F31" s="98"/>
-      <c r="G31" s="98"/>
-      <c r="H31" s="98"/>
-      <c r="I31" s="98"/>
-      <c r="J31" s="98"/>
-    </row>
-    <row r="32" spans="2:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="86"/>
-      <c r="C32" s="98"/>
-      <c r="D32" s="98"/>
-      <c r="E32" s="98"/>
-      <c r="F32" s="98"/>
-      <c r="G32" s="98"/>
-      <c r="H32" s="98"/>
-      <c r="I32" s="98"/>
-      <c r="J32" s="98"/>
-    </row>
-    <row r="33" spans="2:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="86"/>
-      <c r="C33" s="98"/>
-      <c r="D33" s="98"/>
-      <c r="E33" s="98"/>
-      <c r="F33" s="98"/>
-      <c r="G33" s="98"/>
-      <c r="H33" s="98"/>
-      <c r="I33" s="98"/>
-      <c r="J33" s="98"/>
-    </row>
-    <row r="34" spans="2:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="86"/>
-      <c r="C34" s="98"/>
-      <c r="D34" s="98" t="str">
+      <c r="F14" s="96" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="2:30">
+      <c r="B15" s="81"/>
+    </row>
+    <row r="16" spans="2:30">
+      <c r="B16" s="81"/>
+    </row>
+    <row r="17" spans="2:10">
+      <c r="B17" s="81"/>
+      <c r="D17" s="91" t="str">
         <f>Dashboard!C11</f>
         <v>output.passenger_kms</v>
       </c>
-      <c r="E34" s="98">
-        <f>E30*E12</f>
-        <v>9.1047924248184948</v>
-      </c>
-      <c r="F34" s="98" t="s">
-        <v>55</v>
-      </c>
-      <c r="G34" s="98"/>
-      <c r="H34" s="69"/>
-      <c r="I34" s="112"/>
-      <c r="J34" s="98"/>
-    </row>
-    <row r="35" spans="2:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="86"/>
-      <c r="C35" s="98"/>
-      <c r="D35" s="98"/>
-      <c r="E35" s="98"/>
-      <c r="F35" s="98"/>
-      <c r="G35" s="98"/>
-      <c r="J35" s="98"/>
-    </row>
-    <row r="36" spans="2:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="86"/>
-      <c r="C36" s="98"/>
-      <c r="D36" s="98"/>
-      <c r="E36" s="98"/>
-      <c r="F36" s="98"/>
-      <c r="G36" s="98"/>
-      <c r="J36" s="98"/>
-    </row>
-    <row r="37" spans="2:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="86"/>
-      <c r="C37" s="98"/>
-      <c r="D37" s="98"/>
-      <c r="E37" s="98"/>
-      <c r="F37" s="98"/>
-      <c r="G37" s="98"/>
-      <c r="J37" s="98"/>
-    </row>
-    <row r="38" spans="2:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="86"/>
-    </row>
-    <row r="39" spans="2:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="86"/>
-    </row>
-    <row r="40" spans="2:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="86"/>
-    </row>
-    <row r="41" spans="2:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="86"/>
-    </row>
-    <row r="42" spans="2:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="86"/>
-    </row>
-    <row r="43" spans="2:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="86"/>
-    </row>
-    <row r="44" spans="2:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="86"/>
-    </row>
-    <row r="45" spans="2:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="86"/>
-    </row>
-    <row r="46" spans="2:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="86"/>
-    </row>
-    <row r="47" spans="2:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="86"/>
-    </row>
-    <row r="48" spans="2:10" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="86"/>
-    </row>
-    <row r="49" spans="2:2" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="86"/>
-    </row>
-    <row r="50" spans="2:2" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="86"/>
-    </row>
-    <row r="51" spans="2:2" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="86"/>
-    </row>
-    <row r="52" spans="2:2" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="86"/>
-    </row>
-    <row r="53" spans="2:2" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="86"/>
-    </row>
-    <row r="54" spans="2:2" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="86"/>
-    </row>
-    <row r="55" spans="2:2" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="86"/>
-    </row>
-    <row r="56" spans="2:2" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="86"/>
-    </row>
-    <row r="57" spans="2:2" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B57" s="86"/>
-    </row>
-    <row r="58" spans="2:2" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="86"/>
-    </row>
-    <row r="59" spans="2:2" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="86"/>
-    </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B60" s="86"/>
-    </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B61" s="86"/>
-    </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B62" s="86"/>
-    </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B63" s="86"/>
-    </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B64" s="86"/>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B65" s="86"/>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B66" s="86"/>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B67" s="86"/>
-    </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B68" s="86"/>
-    </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B69" s="86"/>
-    </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B70" s="86"/>
-    </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B71" s="86"/>
-    </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B72" s="86"/>
-    </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B73" s="86"/>
-    </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B74" s="86"/>
-    </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B75" s="86"/>
-    </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B76" s="86"/>
-    </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B77" s="86"/>
-    </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B78" s="86"/>
-    </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B79" s="86"/>
-    </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B80" s="86"/>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B81" s="86"/>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B82" s="86"/>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B83" s="86"/>
+      <c r="E17" s="91">
+        <f>ROUND(E12*E14,6)</f>
+        <v>2.5677050000000001</v>
+      </c>
+      <c r="F17" s="91" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" s="91"/>
+    </row>
+    <row r="18" spans="2:10">
+      <c r="B18" s="81"/>
+    </row>
+    <row r="19" spans="2:10">
+      <c r="B19" s="81"/>
+    </row>
+    <row r="20" spans="2:10">
+      <c r="B20" s="81"/>
+    </row>
+    <row r="21" spans="2:10">
+      <c r="B21" s="81"/>
+    </row>
+    <row r="22" spans="2:10">
+      <c r="B22" s="81"/>
+    </row>
+    <row r="23" spans="2:10" ht="306" customHeight="1">
+      <c r="B23" s="81"/>
+    </row>
+    <row r="24" spans="2:10">
+      <c r="B24" s="81"/>
+      <c r="C24" s="90"/>
+      <c r="D24" s="90"/>
+      <c r="E24" s="90"/>
+      <c r="F24" s="90"/>
+      <c r="G24" s="90"/>
+      <c r="H24" s="90"/>
+      <c r="I24" s="90"/>
+      <c r="J24" s="111"/>
+    </row>
+    <row r="25" spans="2:10" s="90" customFormat="1">
+      <c r="B25" s="81"/>
+      <c r="J25" s="91"/>
+    </row>
+    <row r="26" spans="2:10" s="90" customFormat="1">
+      <c r="B26" s="81"/>
+      <c r="J26" s="91"/>
+    </row>
+    <row r="27" spans="2:10" s="90" customFormat="1">
+      <c r="B27" s="81"/>
+      <c r="J27" s="91"/>
+    </row>
+    <row r="28" spans="2:10" s="90" customFormat="1">
+      <c r="B28" s="81"/>
+      <c r="J28" s="91"/>
+    </row>
+    <row r="29" spans="2:10" s="90" customFormat="1">
+      <c r="B29" s="81"/>
+      <c r="J29" s="91"/>
+    </row>
+    <row r="30" spans="2:10" s="90" customFormat="1">
+      <c r="B30" s="81"/>
+      <c r="J30" s="91"/>
+    </row>
+    <row r="31" spans="2:10" s="90" customFormat="1">
+      <c r="B31" s="81"/>
+      <c r="J31" s="91"/>
+    </row>
+    <row r="32" spans="2:10" s="90" customFormat="1">
+      <c r="B32" s="81"/>
+      <c r="J32" s="91"/>
+    </row>
+    <row r="33" spans="2:10" s="90" customFormat="1">
+      <c r="B33" s="81"/>
+      <c r="J33" s="91"/>
+    </row>
+    <row r="34" spans="2:10" s="90" customFormat="1">
+      <c r="B34" s="81"/>
+      <c r="J34" s="91"/>
+    </row>
+    <row r="35" spans="2:10" s="90" customFormat="1">
+      <c r="B35" s="81"/>
+      <c r="C35" s="91"/>
+      <c r="D35" s="91"/>
+      <c r="E35" s="91"/>
+      <c r="F35" s="91"/>
+      <c r="G35" s="91"/>
+      <c r="J35" s="91"/>
+    </row>
+    <row r="36" spans="2:10" s="90" customFormat="1">
+      <c r="B36" s="81"/>
+      <c r="C36" s="91"/>
+      <c r="D36" s="91"/>
+      <c r="E36" s="91"/>
+      <c r="F36" s="91"/>
+      <c r="G36" s="91"/>
+      <c r="J36" s="91"/>
+    </row>
+    <row r="37" spans="2:10" s="90" customFormat="1">
+      <c r="B37" s="81"/>
+      <c r="C37" s="91"/>
+      <c r="D37" s="91"/>
+      <c r="E37" s="91"/>
+      <c r="F37" s="91"/>
+      <c r="G37" s="91"/>
+      <c r="J37" s="91"/>
+    </row>
+    <row r="38" spans="2:10" s="90" customFormat="1">
+      <c r="B38" s="81"/>
+    </row>
+    <row r="39" spans="2:10" s="90" customFormat="1">
+      <c r="B39" s="81"/>
+    </row>
+    <row r="40" spans="2:10" s="90" customFormat="1">
+      <c r="B40" s="81"/>
+    </row>
+    <row r="41" spans="2:10" s="90" customFormat="1">
+      <c r="B41" s="81"/>
+    </row>
+    <row r="42" spans="2:10" s="90" customFormat="1">
+      <c r="B42" s="81"/>
+    </row>
+    <row r="43" spans="2:10" s="90" customFormat="1">
+      <c r="B43" s="81"/>
+    </row>
+    <row r="44" spans="2:10" s="90" customFormat="1">
+      <c r="B44" s="81"/>
+    </row>
+    <row r="45" spans="2:10" s="90" customFormat="1">
+      <c r="B45" s="81"/>
+    </row>
+    <row r="46" spans="2:10" s="90" customFormat="1">
+      <c r="B46" s="81"/>
+    </row>
+    <row r="47" spans="2:10" s="90" customFormat="1">
+      <c r="B47" s="81"/>
+    </row>
+    <row r="48" spans="2:10" s="90" customFormat="1">
+      <c r="B48" s="81"/>
+    </row>
+    <row r="49" spans="2:2" s="90" customFormat="1">
+      <c r="B49" s="81"/>
+    </row>
+    <row r="50" spans="2:2" s="90" customFormat="1">
+      <c r="B50" s="81"/>
+    </row>
+    <row r="51" spans="2:2" s="90" customFormat="1">
+      <c r="B51" s="81"/>
+    </row>
+    <row r="52" spans="2:2" s="90" customFormat="1">
+      <c r="B52" s="81"/>
+    </row>
+    <row r="53" spans="2:2" s="90" customFormat="1">
+      <c r="B53" s="81"/>
+    </row>
+    <row r="54" spans="2:2" s="90" customFormat="1">
+      <c r="B54" s="81"/>
+    </row>
+    <row r="55" spans="2:2" s="90" customFormat="1">
+      <c r="B55" s="81"/>
+    </row>
+    <row r="56" spans="2:2" s="90" customFormat="1">
+      <c r="B56" s="81"/>
+    </row>
+    <row r="57" spans="2:2" s="90" customFormat="1">
+      <c r="B57" s="81"/>
+    </row>
+    <row r="58" spans="2:2" s="90" customFormat="1">
+      <c r="B58" s="81"/>
+    </row>
+    <row r="59" spans="2:2" s="90" customFormat="1">
+      <c r="B59" s="81"/>
+    </row>
+    <row r="60" spans="2:2">
+      <c r="B60" s="81"/>
+    </row>
+    <row r="61" spans="2:2">
+      <c r="B61" s="81"/>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62" s="81"/>
+    </row>
+    <row r="63" spans="2:2">
+      <c r="B63" s="81"/>
+    </row>
+    <row r="64" spans="2:2">
+      <c r="B64" s="81"/>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65" s="81"/>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" s="81"/>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67" s="81"/>
+    </row>
+    <row r="68" spans="2:2">
+      <c r="B68" s="81"/>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69" s="81"/>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" s="81"/>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71" s="81"/>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72" s="81"/>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73" s="81"/>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" s="81"/>
+    </row>
+    <row r="75" spans="2:2">
+      <c r="B75" s="81"/>
+    </row>
+    <row r="76" spans="2:2">
+      <c r="B76" s="81"/>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77" s="81"/>
+    </row>
+    <row r="78" spans="2:2">
+      <c r="B78" s="81"/>
+    </row>
+    <row r="79" spans="2:2">
+      <c r="B79" s="81"/>
+    </row>
+    <row r="80" spans="2:2">
+      <c r="B80" s="81"/>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81" s="81"/>
+    </row>
+    <row r="82" spans="2:2">
+      <c r="B82" s="81"/>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="2">
